--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0DDE9E-2EFB-4D36-B58C-B90357F210C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E8FE22-98FE-480F-AA3E-D9DBD2358D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2287,26 +2287,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B33" s="14">
+        <v>400</v>
+      </c>
+      <c r="C33" s="14">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>40</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>320</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E8FE22-98FE-480F-AA3E-D9DBD2358D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65356F2A-A7F7-4BD5-993D-CBD876FAE46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>good feeling for today</t>
+  </si>
+  <si>
+    <t>Feeling good but something else</t>
   </si>
 </sst>
 </file>
@@ -2333,26 +2336,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B34" s="14">
+        <v>360</v>
+      </c>
+      <c r="C34" s="14">
+        <v>15</v>
+      </c>
+      <c r="D34" s="14">
+        <v>35</v>
+      </c>
+      <c r="E34" s="14">
+        <v>20</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>260</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65356F2A-A7F7-4BD5-993D-CBD876FAE46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B77763-D4D0-4E9A-BEF0-624BCEFBFC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2382,26 +2382,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B35" s="14">
+        <v>370</v>
+      </c>
+      <c r="C35" s="14">
+        <v>20</v>
+      </c>
+      <c r="D35" s="14">
+        <v>20</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>300</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B77763-D4D0-4E9A-BEF0-624BCEFBFC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B62169-C393-439C-86A8-6BE33AEA3A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2428,26 +2428,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B36" s="14">
+        <v>300</v>
+      </c>
+      <c r="C36" s="14">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14">
+        <v>45</v>
+      </c>
+      <c r="E36" s="14">
+        <v>30</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>300</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>435</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B62169-C393-439C-86A8-6BE33AEA3A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1254874-DB11-47C8-9F56-D79EE46595A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2474,26 +2474,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B37" s="14">
+        <v>360</v>
+      </c>
+      <c r="C37" s="14">
+        <v>20</v>
+      </c>
+      <c r="D37" s="14">
+        <v>35</v>
+      </c>
+      <c r="E37" s="14">
+        <v>20</v>
+      </c>
+      <c r="F37" s="14">
+        <v>150</v>
+      </c>
+      <c r="G37" s="14">
+        <v>3</v>
+      </c>
+      <c r="H37" s="14">
+        <v>350</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>935</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>505</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1254874-DB11-47C8-9F56-D79EE46595A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA0DD79-654C-44A2-832B-D56C9B3C18A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2520,26 +2520,46 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
+      <c r="A38" s="13">
+        <v>46276</v>
+      </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="D38" s="14">
+        <v>25</v>
+      </c>
+      <c r="E38" s="14">
+        <v>20</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>300</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>595</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>845</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA0DD79-654C-44A2-832B-D56C9B3C18A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE74DED4-E3EE-446D-84E7-75E3709C75AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2523,8 +2523,12 @@
       <c r="A38" s="13">
         <v>46276</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
+      <c r="B38" s="14">
+        <v>350</v>
+      </c>
+      <c r="C38" s="14">
+        <v>20</v>
+      </c>
       <c r="D38" s="14">
         <v>25</v>
       </c>
@@ -2542,11 +2546,11 @@
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>595</v>
+        <v>965</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>845</v>
+        <v>475</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>49</v>
@@ -2562,48 +2566,96 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B39" s="14">
+        <v>400</v>
+      </c>
+      <c r="C39" s="14">
+        <v>20</v>
+      </c>
+      <c r="D39" s="14">
+        <v>30</v>
+      </c>
+      <c r="E39" s="14">
+        <v>15</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>400</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>865</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>575</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B40" s="14">
+        <v>360</v>
+      </c>
+      <c r="C40" s="14">
+        <v>10</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>300</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE74DED4-E3EE-446D-84E7-75E3709C75AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8031A35C-3AAB-488A-809F-805D6983DB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2658,26 +2658,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B41" s="14">
+        <v>300</v>
+      </c>
+      <c r="C41" s="14">
+        <v>20</v>
+      </c>
+      <c r="D41" s="14">
+        <v>50</v>
+      </c>
+      <c r="E41" s="14">
+        <v>30</v>
+      </c>
+      <c r="F41" s="14">
+        <v>6</v>
+      </c>
+      <c r="G41" s="14">
+        <v>300</v>
+      </c>
+      <c r="H41" s="14">
+        <v>280</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>686</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>754</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8031A35C-3AAB-488A-809F-805D6983DB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF6CBBB-811F-453F-AD59-3971081FED99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2704,26 +2704,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B42" s="14">
+        <v>360</v>
+      </c>
+      <c r="C42" s="14">
+        <v>25</v>
+      </c>
+      <c r="D42" s="14">
+        <v>25</v>
+      </c>
+      <c r="E42" s="14">
+        <v>20</v>
+      </c>
+      <c r="F42" s="14">
+        <v>7</v>
+      </c>
+      <c r="G42" s="14">
+        <v>350</v>
+      </c>
+      <c r="H42" s="14">
+        <v>300</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>737</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>703</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF6CBBB-811F-453F-AD59-3971081FED99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8960F2-F1BC-4F4D-8E94-DAF18D48EDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2674,21 +2674,21 @@
         <v>30</v>
       </c>
       <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
         <v>6</v>
-      </c>
-      <c r="G41" s="14">
-        <v>300</v>
       </c>
       <c r="H41" s="14">
         <v>280</v>
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>686</v>
+        <v>980</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>754</v>
+        <v>460</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>49</v>
@@ -2720,21 +2720,21 @@
         <v>20</v>
       </c>
       <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
         <v>7</v>
-      </c>
-      <c r="G42" s="14">
-        <v>350</v>
       </c>
       <c r="H42" s="14">
         <v>300</v>
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>737</v>
+        <v>1080</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>703</v>
+        <v>360</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>56</v>
@@ -2750,26 +2750,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B43" s="14">
+        <v>380</v>
+      </c>
+      <c r="C43" s="14">
+        <v>20</v>
+      </c>
+      <c r="D43" s="14">
+        <v>45</v>
+      </c>
+      <c r="E43" s="14">
+        <v>30</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>360</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1135</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>305</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8960F2-F1BC-4F4D-8E94-DAF18D48EDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB9E52C-33D8-4F33-909D-74050A6633F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2796,26 +2796,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B44" s="14">
+        <v>340</v>
+      </c>
+      <c r="C44" s="14">
+        <v>10</v>
+      </c>
+      <c r="D44" s="14">
+        <v>45</v>
+      </c>
+      <c r="E44" s="14">
+        <v>20</v>
+      </c>
+      <c r="F44" s="14">
+        <v>150</v>
+      </c>
+      <c r="G44" s="14">
+        <v>3</v>
+      </c>
+      <c r="H44" s="14">
+        <v>300</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>865</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>575</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB9E52C-33D8-4F33-909D-74050A6633F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023BD82F-549E-436A-8BCE-DC548E8104EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2842,26 +2842,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B45" s="14">
+        <v>350</v>
+      </c>
+      <c r="C45" s="14">
+        <v>20</v>
+      </c>
+      <c r="D45" s="14">
+        <v>150</v>
+      </c>
+      <c r="E45" s="14">
+        <v>45</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>250</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1065</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>375</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023BD82F-549E-436A-8BCE-DC548E8104EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E457AC4-26E6-4E57-A04D-CF68E1D40236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Feeling good but something else</t>
+  </si>
+  <si>
+    <t>today I am complete analytical CA and I am very happy .</t>
   </si>
 </sst>
 </file>
@@ -2887,27 +2890,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+    <row r="46" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A46" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B46" s="14">
+        <v>400</v>
+      </c>
+      <c r="C46" s="14">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14">
+        <v>130</v>
+      </c>
+      <c r="E46" s="14">
+        <v>50</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>300</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E457AC4-26E6-4E57-A04D-CF68E1D40236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BEEE74-919F-415B-82C3-9DCD41D93BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2937,26 +2937,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B47" s="14">
+        <v>500</v>
+      </c>
+      <c r="C47" s="14">
+        <v>30</v>
+      </c>
+      <c r="D47" s="14">
+        <v>80</v>
+      </c>
+      <c r="E47" s="14">
+        <v>35</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>380</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>415</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BEEE74-919F-415B-82C3-9DCD41D93BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9648A6-36C0-4FCF-8FC7-2EA0C2F4B69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2983,26 +2983,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B48" s="14">
+        <v>480</v>
+      </c>
+      <c r="C48" s="14">
+        <v>20</v>
+      </c>
+      <c r="D48" s="14">
+        <v>70</v>
+      </c>
+      <c r="E48" s="14">
+        <v>30</v>
+      </c>
+      <c r="F48" s="14">
+        <v>300</v>
+      </c>
+      <c r="G48" s="14">
+        <v>6</v>
+      </c>
+      <c r="H48" s="14">
+        <v>300</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9648A6-36C0-4FCF-8FC7-2EA0C2F4B69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB8F055-66D6-4BA0-B819-EA1D46B2F2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3029,26 +3029,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B49" s="14">
+        <v>520</v>
+      </c>
+      <c r="C49" s="14">
+        <v>10</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>25</v>
+      </c>
+      <c r="F49" s="14">
+        <v>350</v>
+      </c>
+      <c r="G49" s="14">
+        <v>7</v>
+      </c>
+      <c r="H49" s="14">
+        <v>300</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1325</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>115</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB8F055-66D6-4BA0-B819-EA1D46B2F2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCDAB38-F07D-47BD-8A97-9889CF4D22C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2125,21 +2125,21 @@
         <v>30</v>
       </c>
       <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
         <v>6</v>
-      </c>
-      <c r="G29" s="14">
-        <v>360</v>
       </c>
       <c r="H29" s="14">
         <v>230</v>
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>756</v>
+        <v>1050</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>684</v>
+        <v>390</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>49</v>
@@ -3075,26 +3075,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B50" s="14">
+        <v>540</v>
+      </c>
+      <c r="C50" s="14">
+        <v>15</v>
+      </c>
+      <c r="D50" s="14">
+        <v>70</v>
+      </c>
+      <c r="E50" s="14">
+        <v>30</v>
+      </c>
+      <c r="F50" s="14">
+        <v>300</v>
+      </c>
+      <c r="G50" s="14">
+        <v>6</v>
+      </c>
+      <c r="H50" s="14">
+        <v>310</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1265</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>175</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCDAB38-F07D-47BD-8A97-9889CF4D22C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4746E25-E8E0-48FD-B309-7A05E0D3F74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3121,26 +3121,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B51" s="14">
+        <v>570</v>
+      </c>
+      <c r="C51" s="14">
+        <v>30</v>
+      </c>
+      <c r="D51" s="14">
+        <v>130</v>
+      </c>
+      <c r="E51" s="14">
+        <v>45</v>
+      </c>
+      <c r="F51" s="14">
+        <v>100</v>
+      </c>
+      <c r="G51" s="14">
+        <v>2</v>
+      </c>
+      <c r="H51" s="14">
+        <v>350</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1225</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>215</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4746E25-E8E0-48FD-B309-7A05E0D3F74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA727B83-7134-4BB5-97E4-32927F228DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3167,26 +3167,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B52" s="14">
+        <v>480</v>
+      </c>
+      <c r="C52" s="14">
+        <v>20</v>
+      </c>
+      <c r="D52" s="14">
+        <v>80</v>
+      </c>
+      <c r="E52" s="14">
+        <v>25</v>
+      </c>
+      <c r="F52" s="14">
+        <v>250</v>
+      </c>
+      <c r="G52" s="14">
+        <v>5</v>
+      </c>
+      <c r="H52" s="14">
+        <v>310</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1165</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>275</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA727B83-7134-4BB5-97E4-32927F228DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4231184-E91F-40A3-A205-9379AF4E549D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3213,26 +3213,50 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B53" s="14">
+        <v>500</v>
+      </c>
+      <c r="C53" s="14">
+        <v>10</v>
+      </c>
+      <c r="D53" s="14">
+        <v>50</v>
+      </c>
+      <c r="E53" s="14">
+        <v>20</v>
+      </c>
+      <c r="F53" s="14">
+        <v>150</v>
+      </c>
+      <c r="G53" s="14">
+        <v>3</v>
+      </c>
+      <c r="H53" s="14">
+        <v>400</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4231184-E91F-40A3-A205-9379AF4E549D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C66DD71-A1E9-4055-B7E0-8A99AB27042D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3259,26 +3259,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B54" s="14">
+        <v>480</v>
+      </c>
+      <c r="C54" s="14">
+        <v>20</v>
+      </c>
+      <c r="D54" s="14">
+        <v>130</v>
+      </c>
+      <c r="E54" s="14">
+        <v>50</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>380</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C66DD71-A1E9-4055-B7E0-8A99AB27042D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797FBD84-F7D0-49FA-BCE8-BFEA3EE16DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3305,26 +3305,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B55" s="14">
+        <v>500</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <v>20</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>580</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797FBD84-F7D0-49FA-BCE8-BFEA3EE16DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBACF5DA-948D-4ABC-A1E6-E6E4AB9AE74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3351,26 +3351,50 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B56" s="14">
+        <v>520</v>
+      </c>
+      <c r="C56" s="14">
+        <v>10</v>
+      </c>
+      <c r="D56" s="14">
+        <v>25</v>
+      </c>
+      <c r="E56" s="14">
+        <v>20</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>520</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>345</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBACF5DA-948D-4ABC-A1E6-E6E4AB9AE74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD142F85-8424-40AE-92D1-61CB424216A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3397,26 +3397,50 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B57" s="14">
+        <v>540</v>
+      </c>
+      <c r="C57" s="14">
+        <v>20</v>
+      </c>
+      <c r="D57" s="14">
+        <v>45</v>
+      </c>
+      <c r="E57" s="14">
+        <v>30</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>480</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1115</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>325</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD142F85-8424-40AE-92D1-61CB424216A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDE3F9C-D4EB-4DF9-8ECF-A293C01F87D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>today I am complete analytical CA and I am very happy .</t>
+  </si>
+  <si>
+    <t>In this day I am going to visiti golden temple in amritsar</t>
+  </si>
+  <si>
+    <t>I am return this day .</t>
   </si>
 </sst>
 </file>
@@ -3442,49 +3448,97 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+    <row r="58" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B58" s="14">
+        <v>400</v>
+      </c>
+      <c r="C58" s="14">
+        <v>30</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>600</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B59" s="14">
+        <v>560</v>
+      </c>
+      <c r="C59" s="14">
+        <v>45</v>
+      </c>
+      <c r="D59" s="14">
+        <v>0</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>580</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>255</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDE3F9C-D4EB-4DF9-8ECF-A293C01F87D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D5FF46-2E25-43CC-9568-A8A91FC4A801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>I am return this day .</t>
+  </si>
+  <si>
+    <t>today I am start study feeling good</t>
   </si>
 </sst>
 </file>
@@ -3540,27 +3543,51 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+    <row r="60" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A60" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B60" s="14">
+        <v>520</v>
+      </c>
+      <c r="C60" s="14">
+        <v>25</v>
+      </c>
+      <c r="D60" s="14">
+        <v>50</v>
+      </c>
+      <c r="E60" s="14">
+        <v>30</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>520</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>295</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D5FF46-2E25-43CC-9568-A8A91FC4A801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AC8AD4-6BEC-465E-BFFC-5BFB8BE8533D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>today I am start study feeling good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I am complete my python mini project </t>
   </si>
 </sst>
 </file>
@@ -3589,27 +3592,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+    <row r="61" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B61" s="14">
+        <v>500</v>
+      </c>
+      <c r="C61" s="14">
+        <v>10</v>
+      </c>
+      <c r="D61" s="14">
+        <v>210</v>
+      </c>
+      <c r="E61" s="14">
+        <v>70</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>520</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AC8AD4-6BEC-465E-BFFC-5BFB8BE8533D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9E2AFF-E057-4D46-864A-58F9C00A62F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3639,26 +3639,50 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B62" s="14">
+        <v>480</v>
+      </c>
+      <c r="C62" s="14">
+        <v>20</v>
+      </c>
+      <c r="D62" s="14">
+        <v>70</v>
+      </c>
+      <c r="E62" s="14">
+        <v>30</v>
+      </c>
+      <c r="F62" s="14">
+        <v>300</v>
+      </c>
+      <c r="G62" s="14">
+        <v>6</v>
+      </c>
+      <c r="H62" s="14">
+        <v>420</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9E2AFF-E057-4D46-864A-58F9C00A62F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2D59DE-1A78-4BBD-A275-69C67A6EFD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3685,26 +3685,50 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B63" s="14">
+        <v>430</v>
+      </c>
+      <c r="C63" s="14">
+        <v>30</v>
+      </c>
+      <c r="D63" s="14">
+        <v>45</v>
+      </c>
+      <c r="E63" s="14">
+        <v>30</v>
+      </c>
+      <c r="F63" s="14">
+        <v>350</v>
+      </c>
+      <c r="G63" s="14">
+        <v>7</v>
+      </c>
+      <c r="H63" s="14">
+        <v>430</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1315</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>125</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2D59DE-1A78-4BBD-A275-69C67A6EFD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C616B6-E3FD-4299-9979-F9A3AEFEA70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3731,26 +3731,50 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B64" s="14">
+        <v>460</v>
+      </c>
+      <c r="C64" s="14">
+        <v>20</v>
+      </c>
+      <c r="D64" s="14">
+        <v>30</v>
+      </c>
+      <c r="E64" s="14">
+        <v>40</v>
+      </c>
+      <c r="F64" s="14">
+        <v>350</v>
+      </c>
+      <c r="G64" s="14">
+        <v>7</v>
+      </c>
+      <c r="H64" s="14">
+        <v>300</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C616B6-E3FD-4299-9979-F9A3AEFEA70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CC5AF1-947B-4562-840B-6BACDA807E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3777,26 +3777,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B65" s="14">
+        <v>500</v>
+      </c>
+      <c r="C65" s="14">
+        <v>10</v>
+      </c>
+      <c r="D65" s="14">
+        <v>50</v>
+      </c>
+      <c r="E65" s="14">
+        <v>30</v>
+      </c>
+      <c r="F65" s="14">
+        <v>150</v>
+      </c>
+      <c r="G65" s="14">
+        <v>3</v>
+      </c>
+      <c r="H65" s="14">
+        <v>470</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CC5AF1-947B-4562-840B-6BACDA807E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A08C34-38B1-40D6-8650-A021CF13558C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3823,26 +3823,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B66" s="14">
+        <v>470</v>
+      </c>
+      <c r="C66" s="14">
+        <v>20</v>
+      </c>
+      <c r="D66" s="14">
+        <v>120</v>
+      </c>
+      <c r="E66" s="14">
+        <v>40</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>380</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A08C34-38B1-40D6-8650-A021CF13558C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69368F81-5F90-41A8-A493-708DCC1D75DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3869,26 +3869,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B67" s="14">
+        <v>530</v>
+      </c>
+      <c r="C67" s="14">
+        <v>20</v>
+      </c>
+      <c r="D67" s="14">
+        <v>60</v>
+      </c>
+      <c r="E67" s="14">
+        <v>30</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>300</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69368F81-5F90-41A8-A493-708DCC1D75DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF11E3C-6670-4222-A19B-24E4B1B235CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3915,26 +3915,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B68" s="14">
+        <v>500</v>
+      </c>
+      <c r="C68" s="14">
+        <v>10</v>
+      </c>
+      <c r="D68" s="14">
+        <v>70</v>
+      </c>
+      <c r="E68" s="14">
+        <v>20</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>400</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF11E3C-6670-4222-A19B-24E4B1B235CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86717432-ED82-4572-87E8-722F353BCFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3961,26 +3961,50 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B69" s="14">
+        <v>450</v>
+      </c>
+      <c r="C69" s="14">
+        <v>20</v>
+      </c>
+      <c r="D69" s="14">
+        <v>120</v>
+      </c>
+      <c r="E69" s="14">
+        <v>0</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>400</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86717432-ED82-4572-87E8-722F353BCFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E9898F-718E-4B24-9F88-268A444EC958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t xml:space="preserve">Today I am complete my python mini project </t>
+  </si>
+  <si>
+    <t>today is c++ midtearm exam</t>
   </si>
 </sst>
 </file>
@@ -4007,26 +4010,50 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B70" s="14">
+        <v>480</v>
+      </c>
+      <c r="C70" s="14">
+        <v>20</v>
+      </c>
+      <c r="D70" s="14">
+        <v>80</v>
+      </c>
+      <c r="E70" s="14">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>300</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E9898F-718E-4B24-9F88-268A444EC958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610F2D33-8DC6-4629-84AD-550E86FB662F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4056,26 +4056,50 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B71" s="14">
+        <v>500</v>
+      </c>
+      <c r="C71" s="14">
+        <v>10</v>
+      </c>
+      <c r="D71" s="14">
+        <v>80</v>
+      </c>
+      <c r="E71" s="14">
+        <v>0</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>380</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610F2D33-8DC6-4629-84AD-550E86FB662F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70C08CD-E231-4ED2-A417-AC44920452D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4102,26 +4102,50 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B72" s="14">
+        <v>520</v>
+      </c>
+      <c r="C72" s="14">
+        <v>10</v>
+      </c>
+      <c r="D72" s="14">
+        <v>120</v>
+      </c>
+      <c r="E72" s="14">
+        <v>0</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>380</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70C08CD-E231-4ED2-A417-AC44920452D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D928DA-C281-44D6-8E2B-B4E8938967E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4148,26 +4148,50 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B73" s="14">
+        <v>450</v>
+      </c>
+      <c r="C73" s="14">
+        <v>20</v>
+      </c>
+      <c r="D73" s="14">
+        <v>90</v>
+      </c>
+      <c r="E73" s="14">
+        <v>25</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>420</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+        <v>435</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D928DA-C281-44D6-8E2B-B4E8938967E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBCB367F-5571-48D1-83C0-7F5EE27B7FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4194,26 +4194,50 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B74" s="14">
+        <v>430</v>
+      </c>
+      <c r="C74" s="14">
+        <v>20</v>
+      </c>
+      <c r="D74" s="14">
+        <v>120</v>
+      </c>
+      <c r="E74" s="14">
+        <v>30</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>400</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBCB367F-5571-48D1-83C0-7F5EE27B7FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707A6411-D6A2-4615-8464-F50F648C5ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4240,26 +4240,50 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B75" s="14">
+        <v>420</v>
+      </c>
+      <c r="C75" s="14">
+        <v>10</v>
+      </c>
+      <c r="D75" s="14">
+        <v>0</v>
+      </c>
+      <c r="E75" s="14">
+        <v>0</v>
+      </c>
+      <c r="F75" s="14">
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>500</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707A6411-D6A2-4615-8464-F50F648C5ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E796A914-2FD0-48BD-9655-4CE7924EF594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4286,26 +4286,50 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B76" s="14">
+        <v>340</v>
+      </c>
+      <c r="C76" s="14">
+        <v>40</v>
+      </c>
+      <c r="D76" s="14">
+        <v>30</v>
+      </c>
+      <c r="E76" s="14">
+        <v>45</v>
+      </c>
+      <c r="F76" s="14">
+        <v>50</v>
+      </c>
+      <c r="G76" s="14">
+        <v>1</v>
+      </c>
+      <c r="H76" s="14">
+        <v>400</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
+        <v>535</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N76" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E796A914-2FD0-48BD-9655-4CE7924EF594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AD20F0-5754-457D-9CA3-3D6BA5878E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4332,26 +4332,50 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B77" s="14">
+        <v>400</v>
+      </c>
+      <c r="C77" s="14">
+        <v>20</v>
+      </c>
+      <c r="D77" s="14">
+        <v>50</v>
+      </c>
+      <c r="E77" s="14">
+        <v>30</v>
+      </c>
+      <c r="F77" s="14">
+        <v>0</v>
+      </c>
+      <c r="G77" s="14">
+        <v>0</v>
+      </c>
+      <c r="H77" s="14">
+        <v>420</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
+        <v>520</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N77" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AD20F0-5754-457D-9CA3-3D6BA5878E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321E3062-14FB-4C13-9E0B-6533BAB7BCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4378,26 +4378,50 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B78" s="14">
+        <v>430</v>
+      </c>
+      <c r="C78" s="14">
+        <v>30</v>
+      </c>
+      <c r="D78" s="14">
+        <v>45</v>
+      </c>
+      <c r="E78" s="14">
+        <v>30</v>
+      </c>
+      <c r="F78" s="14">
+        <v>300</v>
+      </c>
+      <c r="G78" s="14">
+        <v>6</v>
+      </c>
+      <c r="H78" s="14">
+        <v>300</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>1135</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
+        <v>305</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321E3062-14FB-4C13-9E0B-6533BAB7BCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0873412-A75C-4B7C-91D8-557C83FD8705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4424,26 +4424,50 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="A79" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B79" s="14">
+        <v>380</v>
+      </c>
+      <c r="C79" s="14">
+        <v>20</v>
+      </c>
+      <c r="D79" s="14">
+        <v>50</v>
+      </c>
+      <c r="E79" s="14">
+        <v>30</v>
+      </c>
+      <c r="F79" s="14">
+        <v>150</v>
+      </c>
+      <c r="G79" s="14">
+        <v>3</v>
+      </c>
+      <c r="H79" s="14">
+        <v>300</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N79" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0873412-A75C-4B7C-91D8-557C83FD8705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FE72E6-06A8-429D-8F01-CA7002A7C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4470,26 +4470,50 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+      <c r="A80" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B80" s="14">
+        <v>480</v>
+      </c>
+      <c r="C80" s="14">
+        <v>10</v>
+      </c>
+      <c r="D80" s="14">
+        <v>90</v>
+      </c>
+      <c r="E80" s="14">
+        <v>45</v>
+      </c>
+      <c r="F80" s="14">
+        <v>150</v>
+      </c>
+      <c r="G80" s="14">
+        <v>3</v>
+      </c>
+      <c r="H80" s="14">
+        <v>400</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
-      <c r="N80" s="17"/>
+        <v>265</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N80" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FE72E6-06A8-429D-8F01-CA7002A7C122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B200A8-CB75-4A65-93C6-CB68148C7435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4516,26 +4516,50 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="15" t="str">
+      <c r="A81" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B81" s="14">
+        <v>400</v>
+      </c>
+      <c r="C81" s="14">
+        <v>20</v>
+      </c>
+      <c r="D81" s="14">
+        <v>120</v>
+      </c>
+      <c r="E81" s="14">
+        <v>40</v>
+      </c>
+      <c r="F81" s="14">
+        <v>100</v>
+      </c>
+      <c r="G81" s="14">
+        <v>2</v>
+      </c>
+      <c r="H81" s="14">
+        <v>480</v>
+      </c>
+      <c r="I81" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J81" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
-      <c r="N81" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K81" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M81" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N81" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B200A8-CB75-4A65-93C6-CB68148C7435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D795B25-146F-4473-A7D1-3CC377B23622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>today is c++ midtearm exam</t>
+  </si>
+  <si>
+    <t>today I am compleate ac project</t>
   </si>
 </sst>
 </file>
@@ -4562,26 +4565,50 @@
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82" s="13"/>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="15" t="str">
+      <c r="A82" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B82" s="14">
+        <v>500</v>
+      </c>
+      <c r="C82" s="14">
+        <v>20</v>
+      </c>
+      <c r="D82" s="14">
+        <v>200</v>
+      </c>
+      <c r="E82" s="14">
+        <v>50</v>
+      </c>
+      <c r="F82" s="14">
+        <v>0</v>
+      </c>
+      <c r="G82" s="14">
+        <v>0</v>
+      </c>
+      <c r="H82" s="14">
+        <v>400</v>
+      </c>
+      <c r="I82" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J82" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
-      <c r="N82" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K82" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L82" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N82" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D795B25-146F-4473-A7D1-3CC377B23622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDEC57A-BF6B-42A6-9B47-A4007D935D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4611,26 +4611,50 @@
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A83" s="13"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="15" t="str">
+      <c r="A83" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B83" s="14">
+        <v>400</v>
+      </c>
+      <c r="C83" s="14">
+        <v>30</v>
+      </c>
+      <c r="D83" s="14">
+        <v>130</v>
+      </c>
+      <c r="E83" s="14">
+        <v>30</v>
+      </c>
+      <c r="F83" s="14">
+        <v>0</v>
+      </c>
+      <c r="G83" s="14">
+        <v>0</v>
+      </c>
+      <c r="H83" s="14">
+        <v>300</v>
+      </c>
+      <c r="I83" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J83" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
-      <c r="N83" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L83" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M83" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N83" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDEC57A-BF6B-42A6-9B47-A4007D935D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB6F093-F7A6-4259-9FFF-F2C4C9975D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4657,26 +4657,50 @@
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A84" s="13"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="15" t="str">
+      <c r="A84" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B84" s="14">
+        <v>400</v>
+      </c>
+      <c r="C84" s="14">
+        <v>30</v>
+      </c>
+      <c r="D84" s="14">
+        <v>80</v>
+      </c>
+      <c r="E84" s="14">
+        <v>20</v>
+      </c>
+      <c r="F84" s="14">
+        <v>300</v>
+      </c>
+      <c r="G84" s="14">
+        <v>6</v>
+      </c>
+      <c r="H84" s="14">
+        <v>350</v>
+      </c>
+      <c r="I84" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J84" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
-      <c r="N84" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M84" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N84" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB6F093-F7A6-4259-9FFF-F2C4C9975D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEF2AB8-7D88-4615-B577-AA3CEBC62489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4703,26 +4703,50 @@
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A85" s="13"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="15" t="str">
+      <c r="A85" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B85" s="14">
+        <v>300</v>
+      </c>
+      <c r="C85" s="14">
+        <v>20</v>
+      </c>
+      <c r="D85" s="14">
+        <v>45</v>
+      </c>
+      <c r="E85" s="14">
+        <v>20</v>
+      </c>
+      <c r="F85" s="14">
+        <v>300</v>
+      </c>
+      <c r="G85" s="14">
+        <v>6</v>
+      </c>
+      <c r="H85" s="14">
+        <v>400</v>
+      </c>
+      <c r="I85" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="15" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J85" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
-      <c r="N85" s="17"/>
+        <v>355</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L85" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M85" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N85" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEF2AB8-7D88-4615-B577-AA3CEBC62489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC7C062-0D58-48E1-918A-F08CDA41DCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4749,26 +4749,50 @@
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A86" s="13"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="15" t="str">
+      <c r="A86" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B86" s="14">
+        <v>350</v>
+      </c>
+      <c r="C86" s="14">
+        <v>30</v>
+      </c>
+      <c r="D86" s="14">
+        <v>30</v>
+      </c>
+      <c r="E86" s="14">
+        <v>40</v>
+      </c>
+      <c r="F86" s="14">
+        <v>150</v>
+      </c>
+      <c r="G86" s="14">
+        <v>3</v>
+      </c>
+      <c r="H86" s="14">
+        <v>400</v>
+      </c>
+      <c r="I86" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J86" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K86" s="16"/>
-      <c r="L86" s="16"/>
-      <c r="M86" s="16"/>
-      <c r="N86" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K86" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L86" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M86" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N86" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="13"/>

--- a/12617679.xlsx
+++ b/12617679.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC7C062-0D58-48E1-918A-F08CDA41DCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691AA35E-355F-4F51-8BC1-1AAC2A81A693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>today I am compleate ac project</t>
+  </si>
+  <si>
+    <t>2026-1030</t>
   </si>
 </sst>
 </file>
@@ -4795,26 +4798,50 @@
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A87" s="13"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="14"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="14"/>
-      <c r="I87" s="15" t="str">
+      <c r="A87" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B87" s="14">
+        <v>320</v>
+      </c>
+      <c r="C87" s="14">
+        <v>20</v>
+      </c>
+      <c r="D87" s="14">
+        <v>60</v>
+      </c>
+      <c r="E87" s="14">
+        <v>20</v>
+      </c>
+      <c r="F87" s="14">
+        <v>250</v>
+      </c>
+      <c r="G87" s="14">
+        <v>5</v>
+      </c>
+      <c r="H87" s="14">
+        <v>300</v>
+      </c>
+      <c r="I87" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J87" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J87" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K87" s="16"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="16"/>
-      <c r="N87" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K87" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L87" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M87" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N87" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="13"/>
